--- a/sampleprojects/CorporateTax/excel/states/WY_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/WY_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>DT: Determine WY Filing Requirement</t>
   </si>
@@ -82,7 +82,7 @@
     <t>Wyoming domestic corporation - annual report required ($60); Wyoming has NO corporate income tax - only annual report ($60)</t>
   </si>
   <si>
-    <t>set result.wy_annual_report_fee = result.wy_annual_report_fee_domestic; set result.wy_state_tax = 0.0; set apportionment.state_tax = 0.0; add "Wyoming has NO corporate income tax. Domestic corp annual report: $60. Reference: Wyoming Statutes 17-16-1630" to job.audit_trail;</t>
+    <t>set wy_result.annual_report_fee = wy_result.annual_report_fee_domestic; set wy_result.state_tax = 0.0; set apportionment.state_tax = 0.0; add "Wyoming has NO corporate income tax. Domestic corp annual report: $60. Reference: Wyoming Statutes 17-16-1630" to job.audit_trail;</t>
   </si>
   <si>
     <t>X</t>
@@ -91,13 +91,13 @@
     <t>Wyoming foreign corporation - annual report required ($120); Wyoming has NO corporate income tax - only annual report ($120 foreign)</t>
   </si>
   <si>
-    <t>set result.wy_annual_report_fee = result.wy_annual_report_fee_foreign; set result.wy_state_tax = 0.0; set apportionment.state_tax = 0.0; add "Wyoming has NO corporate income tax. Foreign corp annual report: $120. Reference: Wyoming Statutes 17-16-1630" to job.audit_trail;</t>
+    <t>set wy_result.annual_report_fee = wy_result.annual_report_fee_foreign; set wy_result.state_tax = 0.0; set apportionment.state_tax = 0.0; add "Wyoming has NO corporate income tax. Foreign corp annual report: $120. Reference: Wyoming Statutes 17-16-1630" to job.audit_trail;</t>
   </si>
   <si>
     <t>No Wyoming presence - no filing requirement; No Wyoming presence - no filing requirement</t>
   </si>
   <si>
-    <t>set result.wy_annual_report_fee = 0.0; set result.wy_state_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Wyoming presence - no filing required. WY has no corporate income tax anyway. Any payments refunded." to job.audit_trail;</t>
+    <t>set wy_result.annual_report_fee = 0.0; set wy_result.state_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Wyoming presence - no filing required. WY has no corporate income tax anyway. Any payments refunded." to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate WY Income Adjustments</t>
@@ -115,13 +115,13 @@
     <t>Wyoming - no income tax adjustments; Wyoming has NO corporate income tax - no adjustments</t>
   </si>
   <si>
-    <t>set apportionment.state_tax_rate = 0.0; set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set result.wy_no_corporate_tax = true; set result.wy_no_gross_receipts_tax = true; set result.wy_no_franchise_tax = true; add "Wyoming has NO corporate income tax, franchise tax, or gross receipts tax. No adjustments needed." to job.audit_trail;</t>
+    <t>set wy_apportionment.state_tax_rate = 0.0; set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set wy_result.no_corporate_tax = true; set wy_result.no_gross_receipts_tax = true; set wy_result.no_franchise_tax = true; add "Wyoming has NO corporate income tax, franchise tax, or gross receipts tax. No adjustments needed." to job.audit_trail;</t>
   </si>
   <si>
     <t>No Wyoming presence - no adjustments; No Wyoming presence - no adjustments</t>
   </si>
   <si>
-    <t>set apportionment.state_tax_rate = 0.0; set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set result.wy_no_corporate_tax = true; set result.wy_no_gross_receipts_tax = true; set result.wy_no_franchise_tax = true; add "No Wyoming presence - no tax liability (WY has no corporate income tax anyway)." to job.audit_trail;</t>
+    <t>set wy_apportionment.state_tax_rate = 0.0; set apportionment.state_additions = 0.0; set apportionment.state_subtractions = 0.0; set wy_result.no_corporate_tax = true; set wy_result.no_gross_receipts_tax = true; set wy_result.no_franchise_tax = true; add "No Wyoming presence - no tax liability (WY has no corporate income tax anyway)." to job.audit_trail;</t>
   </si>
   <si>
     <t>DT: Calculate WY State Tax</t>
@@ -136,13 +136,13 @@
     <t>Wyoming - $0 corporate tax; Wyoming has NO corporate income tax</t>
   </si>
   <si>
-    <t>set result.wy_state_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "Wyoming State Tax: $0. NO corporate income tax, NO franchise tax, NO gross receipts tax. Any estimated payments refunded. Reference: Wyoming Statutes Title 39" to job.audit_trail;</t>
+    <t>set wy_result.state_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "Wyoming State Tax: $0. NO corporate income tax, NO franchise tax, NO gross receipts tax. Any estimated payments refunded. Reference: Wyoming Statutes Title 39" to job.audit_trail;</t>
   </si>
   <si>
     <t>No Wyoming presence - $0 tax; No Wyoming presence - $0 tax</t>
   </si>
   <si>
-    <t>set result.wy_state_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Wyoming presence - $0 tax. Wyoming has no corporate income tax anyway. Any payments refunded." to job.audit_trail;</t>
+    <t>set wy_result.state_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No Wyoming presence - $0 tax. Wyoming has no corporate income tax anyway. Any payments refunded." to job.audit_trail;</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -187,10 +187,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>wy_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -220,36 +220,12 @@
     <t>Wyoming economic nexus: $100,000 in Wyoming receipts (Wayfair standard, applies to sales tax only)</t>
   </si>
   <si>
-    <t>state_additions</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>Not applicable - Wyoming has no corporate income tax</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>WY</t>
-  </si>
-  <si>
-    <t>Wyoming state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>Not applicable - Wyoming has no corporate income tax to credit</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
     <t>Wyoming has NO corporate income tax, NO gross receipts tax, NO franchise tax</t>
   </si>
   <si>
@@ -265,19 +241,19 @@
     <t>Wyoming economic nexus: 200 or more separate transactions (applies to sales tax only)</t>
   </si>
   <si>
-    <t>result</t>
+    <t>wy_result</t>
   </si>
   <si>
     <t>(7 attributes)</t>
   </si>
   <si>
-    <t>wy_annual_report_fee</t>
+    <t>annual_report_fee</t>
   </si>
   <si>
     <t>Actual annual report fee based on corporation type (domestic or foreign)</t>
   </si>
   <si>
-    <t>wy_annual_report_fee_domestic</t>
+    <t>annual_report_fee_domestic</t>
   </si>
   <si>
     <t>60.0</t>
@@ -286,7 +262,7 @@
     <t>Wyoming annual report filing fee for domestic corporations (2025)</t>
   </si>
   <si>
-    <t>wy_annual_report_fee_foreign</t>
+    <t>annual_report_fee_foreign</t>
   </si>
   <si>
     <t>120.0</t>
@@ -295,7 +271,7 @@
     <t>Wyoming annual report filing fee for foreign corporations (2025)</t>
   </si>
   <si>
-    <t>wy_no_corporate_tax</t>
+    <t>no_corporate_tax</t>
   </si>
   <si>
     <t>boolean</t>
@@ -307,19 +283,19 @@
     <t>Wyoming has NO corporate income tax (always true)</t>
   </si>
   <si>
-    <t>wy_no_franchise_tax</t>
+    <t>no_franchise_tax</t>
   </si>
   <si>
     <t>Wyoming has NO franchise tax (always true)</t>
   </si>
   <si>
-    <t>wy_no_gross_receipts_tax</t>
+    <t>no_gross_receipts_tax</t>
   </si>
   <si>
     <t>Wyoming has NO gross receipts tax (always true)</t>
   </si>
   <si>
-    <t>wy_state_tax</t>
+    <t>state_tax</t>
   </si>
   <si>
     <t>Wyoming state tax liability (always $0 - no corporate income tax)</t>
@@ -2472,14 +2448,14 @@
       <c r="B7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>59</v>
+      <c r="C7" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -2488,7 +2464,7 @@
         <v>61</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -2507,203 +2483,203 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>61</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>61</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>64</v>
+        <v>88</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>14</v>
@@ -2712,7 +2688,7 @@
         <v>61</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>14</v>
@@ -2735,16 +2711,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>87</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>14</v>
@@ -2753,7 +2729,7 @@
         <v>61</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>14</v>
@@ -2776,7 +2752,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>64</v>
@@ -2785,7 +2761,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>14</v>
@@ -2794,7 +2770,7 @@
         <v>61</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>14</v>
@@ -2809,170 +2785,6 @@
         <v>14</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M19" s="7" t="s">
         <v>14</v>
       </c>
     </row>
